--- a/AAII_Financials/Quarterly/RCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>RCI</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3953900</v>
+      </c>
+      <c r="E8" s="3">
         <v>3927300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4501400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3839500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3824400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3461900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3809300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3796600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3721200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3619300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4039700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3764200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3810600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2834400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3066600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2727700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2858400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2631000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2901500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2715600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2590600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2619000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2847400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2809700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2475900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2681700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3081300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3112300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2997600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2761300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2997200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2738900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2827500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2734900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2776600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2713400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2694000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2590500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2696500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2682700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2234300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2233700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2540300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2033900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2092600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1893800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2048900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1912700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2022400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1984300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2276200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1981900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2156800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1614200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1830700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1574100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1681900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1512200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1774600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1530400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1596900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1574600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1617100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1554000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1460400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1633700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1888400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1692900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1701000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1733600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1839600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1561700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1695300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1727700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1708000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1594800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1660300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1316000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1381300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1187700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1719600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1693600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1961200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1805600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1731800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1568200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1760400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1883900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1698800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1635000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1763600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1782300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1653800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1220200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1235900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1153600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1176500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1118900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1126800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1185200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>993700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1044400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1230300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1255800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1015500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1048000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1192900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1419300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1296600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1027700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1157600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1177200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1132200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1007200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1068700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1118500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1033700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1274500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1315200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1495000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>855600</v>
+      </c>
+      <c r="E14" s="3">
         <v>34400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-9500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3564500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>174500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>91100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>59100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>67400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>65800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>104900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>27300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>157500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>250000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>40700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>42700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>61900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>52500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>69800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>74800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>46700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>83200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>33800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>56500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>37600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>33000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>44400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>34800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>30900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>71500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>34200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>19600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>53400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>23100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>43900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>25300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>21500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>397900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>42300</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>840800</v>
+      </c>
+      <c r="E15" s="3">
         <v>874700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>891200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>883100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>868100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>811200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>815900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>856400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>830000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>848500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>887500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>857500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>874500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>466400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>477000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>469300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>471500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>469600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>487200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>475600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>467900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>479000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>515300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>508300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>510100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>501600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>497400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>519800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>486900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>468800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>429300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>405500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>410300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>409500</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>395200</v>
       </c>
       <c r="AL15" s="3">
         <v>395200</v>
       </c>
       <c r="AM15" s="3">
+        <v>395200</v>
+      </c>
+      <c r="AN15" s="3">
         <v>398200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>418700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>426400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>441700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3074400</v>
+      </c>
+      <c r="E17" s="3">
         <v>3107000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3430800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2916200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2960000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2703600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2863400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2768400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2852400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2831400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3161400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2837200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3027500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2082000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2349700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2106100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2206600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2052300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2336600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2053300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2148700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2088100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2188900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2099800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2003400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2151800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2430200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2247600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2218900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2217900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2340400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1997700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2125100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2182300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2126200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2033900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2047300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2128800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2565900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2116500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E18" s="3">
         <v>820300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1070700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>923300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>864500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>758300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>945900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1028200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>868700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>788000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>878400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>927000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>783100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>752400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>717000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>621600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>651800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>578700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>564900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>662200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>441900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>530900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>658500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>709900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>472400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>529900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>651000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>864700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>778700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>543500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>656800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>741200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>702400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>552500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>650400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>679500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>646700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>461700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>130600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>566200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-81000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>51100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-201000</v>
       </c>
-      <c r="G20" s="3">
-        <v>52800</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>49900</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>24300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>29600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>43600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>351100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>139900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-29900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-21500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-16700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>10500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-6000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>17100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-175900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1737200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1776000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1910800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2007300</v>
       </c>
-      <c r="G21" s="3">
-        <v>1679800</v>
-      </c>
       <c r="H21" s="3">
+        <v>1682700</v>
+      </c>
+      <c r="I21" s="3">
         <v>1569600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1737500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1855000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1698800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1592900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1728000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1433400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1632700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1215100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1342700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1068400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1141000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1065100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1066100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1123700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>919900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1015900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1175300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1217400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>986400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1047300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1167200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1376200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1277600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1031600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1092200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1136500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1106600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>983100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1050800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1067200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1073900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>898100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>568500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E22" s="3">
         <v>368900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>369000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>366900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>378300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>374300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>364900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>393100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>391600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>392100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>305200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>409500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>407800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>193600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>344500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>224500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>253500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>184700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>150300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>145900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>141800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>154700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>161700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>159500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>164800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>160200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>159100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>169100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>157000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>140100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>127900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>122100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>128700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>137000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>133200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>134000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>134700</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>139800</v>
       </c>
       <c r="AO22" s="3">
         <v>139800</v>
       </c>
       <c r="AP22" s="3">
+        <v>139800</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-364100</v>
+      </c>
+      <c r="E23" s="3">
         <v>469200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>660000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4321900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>235400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>264400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>497600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>538100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>385800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>247400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>395300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>102700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>514400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>512300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>367300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>402000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>396200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>412400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>494800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>298700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>367200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>480500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>537400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>299000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>368200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>495900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>673200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>616200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>408000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>520600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>602400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>555600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>426100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>511300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>528400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>529100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>324200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-10800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>252700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E24" s="3">
         <v>123900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>171400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>152200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>126800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>69600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>109800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>148800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>97900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>146900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>82100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>136700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>138400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>96900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>99800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>111200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>112500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>131900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>80300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>96100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>133100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>144900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>80000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>91900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>131000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>181600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>147500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>107000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>138500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>170800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>150600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>106100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>139900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>150300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>136200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>86000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>10000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>97600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-468300</v>
+      </c>
+      <c r="E26" s="3">
         <v>345300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>488700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4169700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>108500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>194800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>387800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>389400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>287900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>189100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>248400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-73200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>82300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>377700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>373900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>270400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>302200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>285000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>299800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>363000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>218400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>271100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>347400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>392500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>218900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>276300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>364900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>491600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>468700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>301000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>382100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>431700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>405000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>319900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>371400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>378100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>392900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>238200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>155200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-511200</v>
+      </c>
+      <c r="E27" s="3">
         <v>313800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>512700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4131000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>115100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>194800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>387800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>389400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>287900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>189100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>248400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-73200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>377700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>373900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>270400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>302200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>285000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>299800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>363000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>218400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>271100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>347400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>392500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>218900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>276300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>364900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>491600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>468700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>301000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>382100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>431700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>405000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>319900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>371400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>378100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>392900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>238200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>155200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E32" s="3">
         <v>81000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-51100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>201000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-52800</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-49900</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-24300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-29600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-43600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-351100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-139900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>29900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>21500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>16200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>22400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>8400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>16700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>6000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>17100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-17100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>175900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-511200</v>
+      </c>
+      <c r="E33" s="3">
         <v>313800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>512700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4131000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>115100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>194800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>387800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>389400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>287900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>189100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>248400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-73200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>82300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>377700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>373900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>270400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>302200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>285000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>299800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>363000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>218400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>271100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>347400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>392500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>218900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>276300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>364900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>491600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>468700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>301000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>382100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>431700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>405000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>319900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>371400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>378100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>392900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>238200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>155200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-511200</v>
+      </c>
+      <c r="E35" s="3">
         <v>313800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>512700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4131000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>115100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>194800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>387800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>389400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>287900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>189100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>248400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-73200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>82300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>377700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>373900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>270400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>302200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>285000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>299800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>363000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>218400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>271100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>347400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>392500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>218900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>276300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>364900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>491600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>468700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>301000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>382100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>431700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>405000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>319900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>371400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>378100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>392900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>238200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>155200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,121 +4305,122 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1215400</v>
+      </c>
+      <c r="E41" s="3">
         <v>992900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>980200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1085500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5105400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1864500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>624100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>593700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>329500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>564200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>605800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1868000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>271100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>408700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>340800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>491400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>588200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>529400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1164400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>654500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>601400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1922000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1723400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1408600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1519900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>385200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>217200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>320400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>203200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>308200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>41400</v>
-      </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL41" s="3" t="s">
+      <c r="AK41" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AL41" s="3">
+        <v>0</v>
       </c>
       <c r="AM41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN41" s="3">
-        <v>0</v>
+      <c r="AN41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO41" s="3">
         <v>0</v>
@@ -4341,44 +4428,47 @@
       <c r="AP41" s="3">
         <v>0</v>
       </c>
+      <c r="AQ41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>213400</v>
+      </c>
+      <c r="E42" s="3">
         <v>190600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>72200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>119200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>50600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>190600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>233500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>57000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>76700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>60600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4141300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4160900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4656800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4126000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4066400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3715900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3926100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3764800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3681000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3677700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4113900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3322100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3360500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3144100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3161600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2799900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2758600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2673200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2933300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2686700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2454600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2480800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2622200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1947300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1986200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2416400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2758500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2695200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2627300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2439600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2520000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2201100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2224500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2078500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2124700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1351500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1402100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1336000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1497300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1451200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>389400</v>
+      </c>
+      <c r="E44" s="3">
         <v>330300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>401100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>345300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>402500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>391000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>445500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>349400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>374100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>373700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>345300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>341500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>411600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>410200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>322400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>236800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>333300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>392600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>396100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>294100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>337700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>349100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>370600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>352700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>250300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>332100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>358600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>325800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>364000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>355700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>354700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>278300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>268000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>323700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>174900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>215800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>227400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>242000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>207400</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>944300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1017300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>566000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1051100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>725900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>751400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>378800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>719500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>720400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>929000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>563400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>978000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1032300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>866200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10369600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10053200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10243900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10148300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>456800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>482200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>444800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>599900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>446500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>926100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>744700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>711300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>487300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>498300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>468700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>471100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>537300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>426600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>461500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>660200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>621400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>493400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>292500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>340300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>235100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>346500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6903700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6691900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6919900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6727000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10350800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6913400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5819300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5484300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5181700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5617700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5932000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6509700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5075500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14317000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14194400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13590600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13827200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13802300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4315600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4627400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3891600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4031400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5361300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4949400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4389800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4979600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3989600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3736500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3780300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3469600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3720200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2947500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2979500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3006600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3069900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2019800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1910400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1903700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1974400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2005100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1585800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1563900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1485600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1431600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>945800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1176500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1120300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1031100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1041900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1031700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>885200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1772700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2121300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2138900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2189200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1975700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2171900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2385300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2478000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2543000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2596400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2681300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2541000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2185700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2175300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2333200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2640700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2679500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2430600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2288700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2031300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1875600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1956500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2046100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2213300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1911900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1774900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1723100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1670100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1678600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18510000</v>
+      </c>
+      <c r="E48" s="3">
         <v>18821400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19186500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18822700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18541500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17526000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17425100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18366300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18040400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18115100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18424500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17781600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17892300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11786300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11464200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11168200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11093700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10752500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10858100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10655500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10233600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10495500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10846400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10687000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11024000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11029200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10863900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11325700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10735900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10259400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8965600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>8361300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8544200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8451600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8292700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8053100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7946700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8223100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8257700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8524300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34365900</v>
+      </c>
+      <c r="E49" s="3">
         <v>35055800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35686200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35260500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24827300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23658100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23726100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25360700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25118200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25144000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>25878600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>25600400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26308000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12036900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11985300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11869300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12033000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11850300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12071600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9618500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9338900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9702600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9980600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9836800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10058800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10063600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10001600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10625100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10168100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8539600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8455700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8072100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8362000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8376300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8297200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>8316500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>8331400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>8462800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>8477400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>8482800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1473800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1497300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1094000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1338200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1144500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>811900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>412800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>673600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>529700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>560500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>310500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>736300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>599600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>546900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1135100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1319800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1347900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1231600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1344500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2020000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1187500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1210400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1333900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2247800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2593600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3056200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1366800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1530400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1063400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>964600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1119600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>768100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>898100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>835600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>817900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>807500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1178100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1310600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1393600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1451200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63589200</v>
+      </c>
+      <c r="E54" s="3">
         <v>64447700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65648500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64337500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56593100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50872800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49631000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51638500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>50647000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>51262800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52461300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53060800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52665000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41484500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40968200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39923700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40473700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40021900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31067700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29464400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27248000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28121200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>30063300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29906600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30241500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31461700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28862600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29897200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>28178400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>25521800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>24292500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>22024500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22740300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>22716200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>22691000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>21108800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>21141500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>21623400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>21773200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>22141900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3080800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3213100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3440300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3135900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2863900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2515700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2771000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2754400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2653000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2791500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3062200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2772900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2680900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2164100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2739800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2363400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2194800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2022500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2529100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2196300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1963500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1847900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2100000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1912000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1836300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1910000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2364700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2132300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2199000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2073100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2322800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1999100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1995600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1894000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2181300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1926800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1759300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1801500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2138000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2049600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5506700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5412400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4285500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4181200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2321400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3451500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5033200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4485000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4543200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3657000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2539700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3757500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4346800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4763500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3809400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2952200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2826600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3101400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3025900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3152600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2202900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1857600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2281800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2069900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1860600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2095300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1924200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2579200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2129300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2567300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2401200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1673600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1947500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2259100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2490900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2619600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1534600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1294500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1245300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1391300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4077200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3469500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3606500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3540100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>898200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>966400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>909100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>783900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>808800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>883200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>914000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>723000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>756700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>572100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>479900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>372400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>542400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>650700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>826200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>578500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>802100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>706600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>714200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>631700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>555600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>507100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>361000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>520600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>478200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>575800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>478700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>406900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>504400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>505100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>710700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>340100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>471100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>543100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>544700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>620700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12664600</v>
+      </c>
+      <c r="E60" s="3">
         <v>12095100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11415500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10857300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6083500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6933600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8763300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8023200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8005000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7331700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6649900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7253400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7784300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7499600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7029100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5688000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5563900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5774600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6381200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5927400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4968500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4412100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5095900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4613600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4252500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4512500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4650000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5232100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4806500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5216300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5202800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4079600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4447500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4658300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5122400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4886500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3765000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3639100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3928000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4061600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26672800</v>
+      </c>
+      <c r="E61" s="3">
         <v>26684600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28399400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28098400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>30970200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30883900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28653600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29502200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>29317200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30352600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>32474700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>32069500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30531600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23126200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23239700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24202800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23990600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23145800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13887700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12470400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11951900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12962100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14165800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14456500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15013600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15647600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13614600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13525100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13540800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11235500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10191000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9784900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10237900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10111500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9445500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9418000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11108800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11856900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11777000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11659400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1492100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1445000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>874500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1652000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1888000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1298900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>331500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1160700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1039700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1063400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>324800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1012000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1148600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>543200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3270500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2991600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2925700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3022200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3001400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3269600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3023100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3185100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3394400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3142500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3149200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3294900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3256700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3145400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2841400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2705900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2673700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2499800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2450300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2475200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2544500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2123200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1973600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2023500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2020400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1949000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47498800</v>
+      </c>
+      <c r="E66" s="3">
         <v>47022600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47936000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47372700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43492700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>43478600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42400800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43299200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>42889700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>43428200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>44556000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44953600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43933700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33833500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33539400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32882400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32480100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31942600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23270300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21667400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19943500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20559300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22656200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22212600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22415300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23454900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21521200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21902700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21188700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>19157700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>18067500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16364300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17135800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>17244900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17112400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>16427700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>16847400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17519500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17725400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>17670100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11055600</v>
+      </c>
+      <c r="E72" s="3">
         <v>11961100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12054400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11529300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7754500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7401100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7387900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7673900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7273600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7257100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7450200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7062700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7490600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7446400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7231500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6821900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6791300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6576500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6596600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6155500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5833500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6018900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6121900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5986700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5927100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5910600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5785200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6376200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6693900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6197100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5957100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5471200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5414100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5266500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5270500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4324600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4021700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3845000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3755900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4077000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11660400</v>
+      </c>
+      <c r="E76" s="3">
         <v>12877400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12946400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12163900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8226700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7394200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7230100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8339300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7757300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7834600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7905300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8107200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8731300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7651100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7428800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7041300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7993700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8079300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7797500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7797000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7304500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7561900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7407100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7694000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7826200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8006700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7341400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7994500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6989700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6364100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6225000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5660200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5604500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5471300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5578600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4681100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4294100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4103900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4047800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4471900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-511200</v>
+      </c>
+      <c r="E81" s="3">
         <v>313800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>512700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4131000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>115100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>194800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>387800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>389400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>287900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>189100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>248400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-73200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>82300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>377700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>373900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>270400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>302200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>285000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>299800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>363000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>218400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>271100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>347400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>392500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>218900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>276300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>364900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>491600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>468700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>301000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>382100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>431700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>405000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>319900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>371400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>378100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>392900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>238200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>155200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>766900</v>
+      </c>
+      <c r="E83" s="3">
         <v>715900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>721400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>755000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>729900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>750300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>791300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>751800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>766500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>461900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>475800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>464700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>490700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>517400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>485800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>476600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>485500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>484200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>503400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>483000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>479500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>494100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>533100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>520500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>522600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>518900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>512200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>533900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>504400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>483400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>443700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>412000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>422300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>420100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>406300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>404900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>410100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>434000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>439400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>453300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1068200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1071000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1204900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1087700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1170200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>901700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>788800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1401200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1075500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>871400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1044200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1296600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1234700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>334800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>842800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>886200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>974700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>591100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>849200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>977000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>734800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>509800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>732700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>755900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1121400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>752900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>909100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1081900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>838200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>768300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>799900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>947600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>788900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>666200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>849900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1024800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>612500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>457900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>808900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>910400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-489400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-578900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-795000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-692100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-609300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-680400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-740900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-723200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-729900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-781300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-798100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-751800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-814800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-659300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-784000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-889000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-788000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-661000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-859000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-757000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-520000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-363400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-507600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-386400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-438700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-465500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-590200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-613000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-475000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-630200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-508700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-494600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-455400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-625900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-489700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-335600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-384100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-466300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-436400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-582400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-792300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-560900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3975900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-671600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-688100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-604700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1050700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-787200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-169600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-702300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13653500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-699200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-744200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-553100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-490000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-603400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2585300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1083700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-405000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-464000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-506800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-419400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-470800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-593500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-540300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-600200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1951600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-565000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-561700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-543600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-541300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-556300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-550700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-443500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-511300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-466300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-394900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-477100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,112 +10455,113 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>190100</v>
+      </c>
+      <c r="E96" s="3">
         <v>193400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>196900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>193800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>137800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>128700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>125800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>137700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>133000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>140300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>144600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>195200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>190300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>187000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-186200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-184400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-186200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-183200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-187300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-187400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-182300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-189200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-195800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-194000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-197800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-198600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-199600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-212200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-203800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-190100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-188000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-179500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-185900</v>
       </c>
       <c r="AJ96" s="3">
         <v>-185900</v>
       </c>
       <c r="AK96" s="3">
-        <v>-183800</v>
+        <v>-185900</v>
       </c>
       <c r="AL96" s="3">
         <v>-183800</v>
@@ -10336,7 +10570,7 @@
         <v>-183800</v>
       </c>
       <c r="AN96" s="3">
-        <v>-189800</v>
+        <v>-183800</v>
       </c>
       <c r="AO96" s="3">
         <v>-189800</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>-189800</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-189800</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-246500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-248600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-766500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1025200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2641800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1026200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-117500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-341200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-253500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-110800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2182300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1008300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2578200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>430900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-263500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-531300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-591200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9627100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1101700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-254600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1309500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-43300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>10700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-761200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>972700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-187900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-599400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1224400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-311800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>26600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-354600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-219100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-142300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-277600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-552200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-119800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>25400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-460200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-331900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>239400</v>
+      </c>
+      <c r="E102" s="3">
         <v>30100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-122500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3913400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3140400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1239800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>259800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-228700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1307700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1602700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9840700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>66500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-164900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-198200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-106400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9614700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-634500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>494100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>75200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1263700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>182600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>347300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-110600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1132000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>180900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-117700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>111000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-108500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>264900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>49400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-32400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>21600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>29000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-18600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>16900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-46100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>101400</v>
       </c>
     </row>
